--- a/docs/api/API_DEVELOPMENT_PROGRESS_SIMPLE.xlsx
+++ b/docs/api/API_DEVELOPMENT_PROGRESS_SIMPLE.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API 목록" sheetId="1" r:id="R04856e70fb724301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API 목록" sheetId="1" r:id="Raaf8e17452c540c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -332,19 +332,7 @@
     <x:t xml:space="preserve">void HomeDS402(MMC_HOMEDS402Params HomeDS402Params)</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">DS-402 표준에 따라 특정 단일 축의 호밍(Search Home) 시퀀스를 실행한다.
-호밍 방식(uiHomingMethod, 1~36), 속도, 가속도, 거리/토크 한계, 위치 오프셋을 설정하여 기준점 탐색을 수행한다. StandStill 상태에서만 동작 가능하다.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">DS_402 표준 기반의 호밍 실행</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PrepareLMC_HomeDS402
-LMC_HomeDS402
-LMC_HomeDS402Async
-ReadDs402HomeOutcome
-ReadDs402HomeOutcomeAsync
-(gate OFF)</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">MMC_ReadStatusCmd</x:t>
@@ -1190,7 +1178,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1252,6 +1240,12 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -2048,7 +2042,7 @@
         <x:v>90% 유지: group parameter read 구현. allowlist 한정; raw passthrough/live 미검증</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="99">
+    <x:row r="22" ht="135" customHeight="1">
       <x:c r="A22" s="4">
         <x:v>19</x:v>
       </x:c>
@@ -2056,24 +2050,30 @@
       <x:c r="C22" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="D22" s="22" t="str">
+        <x:v>DS-402 표준 Homing을 단일 축에서 수행한다. 지원 Homing Method는 1..14, 17..30, 33, 34, 37이다. 0x6098 Homing Method, 0x607C Home Offset, 0x6099:01 Home Velocity1, 0x6099:02 Home Velocity2, 0x609A Home Acceleration을 설정한다. Start ACK 뒤 retained outcome을 조회하며 완료 후 Home 진입 전 운전 모드로 복귀한다.</x:v>
+      </x:c>
+      <x:c r="E22" s="22" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="F22" s="1"/>
-      <x:c r="G22" s="1" t="s">
+      <x:c r="F22" s="22"/>
+      <x:c r="G22" s="22" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="H22" s="14" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="I22" s="15" t="s">
-        <x:v>96</x:v>
+      <x:c r="H22" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I22" s="15" t="str">
+        <x:v>PrepareLMC_HomeDS402
+LMC_HomeDS402
+LMC_HomeDS402Async
+ReadDs402HomeOutcome
+ReadDs402HomeOutcomeAsync
+RetireDs402HomeOutcome
+RetireDs402HomeOutcomeAsync</x:v>
       </x:c>
       <x:c r="J22" s="16" t="str">
-        <x:v>50% 유지: SDK/wire+method 37 source 존재. gate FALSE·bit 6 OFF·native 0; 활성화·회복·실축 검증 필요</x:v>
+        <x:v>100% 구현: public API/parameter editor/PLC state machine 완료. Method 37 사용자 실기 확인 완료. moving method 1..14, 17..30, 33, 34는 개별 실축 qualification 대기. production NO-GO.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="66" customHeight="1">
@@ -2081,16 +2081,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="4" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="F23" s="1"/>
       <x:c r="G23" s="1" t="s">
@@ -2100,7 +2100,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I23" s="15" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="J23" s="16" t="str">
         <x:v>활성: 0x2028 상태 read 구현. current image runtime 회귀 필요</x:v>
@@ -2111,16 +2111,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="4" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="E24" s="1" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="F24" s="1"/>
       <x:c r="G24" s="1" t="s">
@@ -2130,7 +2130,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I24" s="15" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="J24" s="16" t="str">
         <x:v>활성: 0x2045 그룹 상태 read 구현. current image runtime 회귀 필요</x:v>
@@ -2141,16 +2141,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="4" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F25" s="1"/>
       <x:c r="G25" s="1" t="s">
@@ -2169,16 +2169,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="4" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
+      <x:c r="E26" s="1" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="F26" s="1"/>
       <x:c r="G26" s="1" t="s">
@@ -2197,16 +2197,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="4" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
-      <x:c r="C27" s="1" t="s">
+      <x:c r="E27" s="1" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="F27" s="1"/>
       <x:c r="G27" s="1" t="s">
@@ -2216,7 +2216,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I27" s="15" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="J27" s="16" t="str">
         <x:v>활성: 0x209F 절대이동 구현. raw DINT와 제한 옵션, current image 실축 회귀 필요</x:v>
@@ -2227,14 +2227,14 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="4" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C28" s="1"/>
       <x:c r="D28" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E28" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
         <x:v>25</x:v>
@@ -2246,7 +2246,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="I28" s="15" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="J28" s="16" t="str">
         <x:v>대체: No.26/27 Ex 경로로 통합. 별도 non-Ex API는 범위 제외</x:v>
@@ -2257,16 +2257,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="4" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>125</x:v>
-      </x:c>
       <x:c r="E29" s="5" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F29" s="1"/>
       <x:c r="G29" s="1" t="s">
@@ -2276,7 +2276,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I29" s="15" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J29" s="16" t="str">
         <x:v>부분 구현: fixed X/Y/Z/U와 제한된 coord/transition/buffer만 지원</x:v>
@@ -2287,16 +2287,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="E30" s="7" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="F30" s="1"/>
       <x:c r="G30" s="1" t="s">
@@ -2306,7 +2306,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I30" s="15" t="s">
-        <x:v>126</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="J30" s="16" t="str">
         <x:v>활성: 단순 overload 구현. raw DINT 배열 사용, current image 실축 회귀 필요</x:v>
@@ -2317,14 +2317,14 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="4" t="s">
-        <x:v>130</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C31" s="1"/>
       <x:c r="D31" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E31" s="7" t="s">
-        <x:v>132</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
         <x:v>25</x:v>
@@ -2336,7 +2336,7 @@
         <x:v>N/A</x:v>
       </x:c>
       <x:c r="I31" s="15" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="J31" s="16" t="str">
         <x:v>대체: No.41 relative Ex로 통합. 별도 non-Ex API는 범위 제외</x:v>
@@ -2347,16 +2347,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="4" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="C32" s="1" t="s">
+      <x:c r="E32" s="1" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="F32" s="1"/>
       <x:c r="G32" s="1" t="s">
@@ -2366,7 +2366,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I32" s="15" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="J32" s="16" t="str">
         <x:v>활성: Reset과 accepted-once recovery 구현. current image fault 회귀 필요</x:v>
@@ -2377,16 +2377,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="4" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
         <x:v>139</x:v>
       </x:c>
-      <x:c r="C33" s="1" t="s">
+      <x:c r="E33" s="1" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>142</x:v>
       </x:c>
       <x:c r="F33" s="1"/>
       <x:c r="G33" s="1" t="s">
@@ -2396,7 +2396,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I33" s="15" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="J33" s="16" t="str">
         <x:v>활성: GroupReset 구현. current image fault 회귀 필요</x:v>
@@ -2407,16 +2407,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="4" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="C34" s="1" t="s">
+      <x:c r="E34" s="1" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="D34" s="1" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="E34" s="1" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="F34" s="1"/>
       <x:c r="G34" s="1" t="s">
@@ -2426,7 +2426,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I34" s="15" t="s">
-        <x:v>148</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="J34" s="16" t="str">
         <x:v>활성: PowerOff 구현. current image 실축 회귀 필요</x:v>
@@ -2437,16 +2437,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="4" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="C35" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>152</x:v>
       </x:c>
       <x:c r="F35" s="1"/>
       <x:c r="G35" s="1" t="s">
@@ -2456,7 +2456,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I35" s="15" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="J35" s="16" t="str">
         <x:v>90% 유지: GroupDisable→UnlockProfile 적응. 의미 차이·전이/회복 재검증 필요</x:v>
@@ -2467,16 +2467,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="4" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>154</x:v>
       </x:c>
-      <x:c r="C36" s="1" t="s">
+      <x:c r="E36" s="1" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="F36" s="1"/>
       <x:c r="G36" s="1" t="s">
@@ -2496,13 +2496,13 @@
       </x:c>
       <x:c r="B37" s="4"/>
       <x:c r="C37" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="F37" s="1"/>
       <x:c r="G37" s="1" t="s">
@@ -2512,7 +2512,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I37" s="15" t="s">
-        <x:v>161</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="J37" s="16" t="str">
         <x:v>90% 유지: D5 0x6061 typed mode read 구현. 과거 4축 CSP 확인, current image live 재검증 필요</x:v>
@@ -2523,16 +2523,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
         <x:v>162</x:v>
-      </x:c>
-      <x:c r="D38" s="1" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>164</x:v>
       </x:c>
       <x:c r="F38" s="1"/>
       <x:c r="G38" s="1" t="s">
@@ -2542,7 +2542,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I38" s="15" t="s">
-        <x:v>165</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="J38" s="16" t="str">
         <x:v>활성: PowerOn 구현. current image 실축 회귀 필요</x:v>
@@ -2553,16 +2553,16 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="4" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="C39" s="1" t="s">
+      <x:c r="E39" s="1" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="D39" s="1" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>169</x:v>
       </x:c>
       <x:c r="F39" s="1"/>
       <x:c r="G39" s="1" t="s">
@@ -2572,7 +2572,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I39" s="15" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="J39" s="16" t="str">
         <x:v>90% 유지: GroupEnable→LASAL LockProfile 적응. 의미 차이와 current image 전이·회복 재검증 필요</x:v>
@@ -2584,16 +2584,16 @@
       </x:c>
       <x:c r="B40" s="4"/>
       <x:c r="C40" s="1" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D40" s="1" t="s">
+      <x:c r="F40" s="1" t="s">
         <x:v>172</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F40" s="1" t="s">
-        <x:v>174</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>38</x:v>
@@ -2612,16 +2612,16 @@
       </x:c>
       <x:c r="B41" s="4"/>
       <x:c r="C41" s="1" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>177</x:v>
-      </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>38</x:v>
@@ -2639,16 +2639,16 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="4" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
         <x:v>178</x:v>
       </x:c>
-      <x:c r="C42" s="1" t="s">
+      <x:c r="E42" s="1" t="s">
         <x:v>179</x:v>
-      </x:c>
-      <x:c r="D42" s="1" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>181</x:v>
       </x:c>
       <x:c r="F42" s="1"/>
       <x:c r="G42" s="1" t="s">
@@ -2658,7 +2658,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I42" s="15" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="J42" s="16" t="str">
         <x:v>90% 유지: 0x202E actual-position read 구현. caller-scaled raw DINT; current image live 재검증 필요</x:v>
@@ -2669,16 +2669,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="4" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="C43" s="1" t="s">
+      <x:c r="E43" s="1" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="D43" s="1" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="E43" s="1" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="F43" s="1"/>
       <x:c r="G43" s="1" t="s">
@@ -2688,7 +2688,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I43" s="15" t="s">
-        <x:v>187</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="J43" s="16" t="str">
         <x:v>활성: 0x20A0 상대이동 구현. 제한 buffer, current image 실축 회귀 필요</x:v>
@@ -2700,16 +2700,16 @@
       </x:c>
       <x:c r="B44" s="4"/>
       <x:c r="C44" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="D44" s="1" t="s">
+      <x:c r="F44" s="1" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="F44" s="1" t="s">
-        <x:v>191</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>44</x:v>
@@ -2718,7 +2718,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I44" s="15" t="s">
-        <x:v>192</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="J44" s="16" t="str">
         <x:v>활성: 0x7D22 그룹 상대이동 구현. Buffered queue live 회귀 필요</x:v>
@@ -2729,16 +2729,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="4" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="C45" s="1" t="s">
+      <x:c r="E45" s="1" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>196</x:v>
       </x:c>
       <x:c r="F45" s="1"/>
       <x:c r="G45" s="1" t="s">
@@ -2748,7 +2748,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I45" s="15" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="J45" s="16" t="str">
         <x:v>활성: Stop과 accepted-once 완료/recovery 구현. current image fault 회귀 필요</x:v>
@@ -2759,16 +2759,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="4" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="C46" s="1" t="s">
+      <x:c r="E46" s="1" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>201</x:v>
       </x:c>
       <x:c r="F46" s="1"/>
       <x:c r="G46" s="1" t="s">
@@ -2778,7 +2778,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I46" s="15" t="s">
-        <x:v>202</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="J46" s="16" t="str">
         <x:v>활성: GroupStop과 stable standby poll 구현. current image PLC 완료 poll 필요</x:v>
@@ -2789,16 +2789,16 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="4" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="C47" s="1" t="s">
+      <x:c r="E47" s="1" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>206</x:v>
       </x:c>
       <x:c r="F47" s="1"/>
       <x:c r="G47" s="1" t="s">
@@ -2808,7 +2808,7 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I47" s="15" t="s">
-        <x:v>207</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="J47" s="16" t="str">
         <x:v>제한 활성: MoveEndless 기반. deceleration=0 제약과 buffer mode 미노출</x:v>
@@ -2819,16 +2819,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="4" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="C48" s="1" t="s">
+      <x:c r="E48" s="1" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="D48" s="1" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="E48" s="1" t="s">
-        <x:v>211</x:v>
       </x:c>
       <x:c r="F48" s="1"/>
       <x:c r="G48" s="1" t="s">
@@ -2848,13 +2848,13 @@
       </x:c>
       <x:c r="B49" s="4"/>
       <x:c r="C49" s="1" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>214</x:v>
       </x:c>
       <x:c r="F49" s="1"/>
       <x:c r="G49" s="1" t="s">
@@ -2864,7 +2864,7 @@
         <x:v>0.9</x:v>
       </x:c>
       <x:c r="I49" s="15" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="J49" s="16" t="str">
         <x:v>90% 유지: 1/2/4-byte SDO read+ticket terminal 구현. 8-byte 미지원; current facade/live 재검증 필요</x:v>
@@ -2876,13 +2876,13 @@
       </x:c>
       <x:c r="B50" s="4"/>
       <x:c r="C50" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F50" s="1"/>
       <x:c r="G50" s="1" t="s">
@@ -2902,13 +2902,13 @@
       </x:c>
       <x:c r="B51" s="4"/>
       <x:c r="C51" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="F51" s="1"/>
       <x:c r="G51" s="1" t="s">
@@ -2918,7 +2918,7 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I51" s="15" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="J51" s="16" t="str">
         <x:v>제한 활성: Real32/4 read 구현. current image live 재확인 필요</x:v>
@@ -2930,13 +2930,13 @@
       </x:c>
       <x:c r="B52" s="4"/>
       <x:c r="C52" s="1" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="D52" s="1" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>222</x:v>
       </x:c>
       <x:c r="F52" s="1"/>
       <x:c r="G52" s="1" t="s">
@@ -2946,7 +2946,7 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I52" s="15" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="J52" s="16" t="str">
         <x:v>제한 활성: Int32/4 read 구현. No.46과 기능 중복, current image 재확인 필요</x:v>
@@ -2957,16 +2957,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="4" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
         <x:v>223</x:v>
       </x:c>
-      <x:c r="C53" s="1" t="s">
+      <x:c r="E53" s="1" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="D53" s="1" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="E53" s="1" t="s">
-        <x:v>226</x:v>
       </x:c>
       <x:c r="F53" s="1"/>
       <x:c r="G53" s="1" t="s">
@@ -2976,7 +2976,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I53" s="15" t="s">
-        <x:v>227</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="J53" s="16" t="str">
         <x:v>비활성: write scaffold만 존재. Int64/8-byte 미지원</x:v>
@@ -2987,16 +2987,16 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B54" s="4" t="s">
-        <x:v>223</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="F54" s="1"/>
       <x:c r="G54" s="1" t="s">
@@ -3006,7 +3006,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I54" s="15" t="s">
-        <x:v>227</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="J54" s="16" t="str">
         <x:v>비활성: write scaffold만 존재. Real64/8-byte 미지원</x:v>
@@ -3017,16 +3017,16 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B55" s="4" t="s">
-        <x:v>223</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="F55" s="1"/>
       <x:c r="G55" s="1" t="s">
@@ -3036,7 +3036,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I55" s="15" t="s">
-        <x:v>232</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="J55" s="16" t="str">
         <x:v>제한 활성: Axis1의 0x2F00:24 Int32/4만 허용. Axis2~4와 다른 target 차단</x:v>
@@ -3048,13 +3048,13 @@
       </x:c>
       <x:c r="B56" s="4"/>
       <x:c r="C56" s="1" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="D56" s="1" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="E56" s="1" t="s">
-        <x:v>235</x:v>
       </x:c>
       <x:c r="F56" s="1"/>
       <x:c r="G56" s="1" t="s">
@@ -3073,16 +3073,16 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B57" s="4" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="C57" s="1" t="s">
+      <x:c r="E57" s="1" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="D57" s="1" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="E57" s="1" t="s">
-        <x:v>239</x:v>
       </x:c>
       <x:c r="F57" s="1"/>
       <x:c r="G57" s="1" t="s">
@@ -3092,7 +3092,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I57" s="15" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="J57" s="16" t="str">
         <x:v>부분 구현: Axis1~4와 6개 semantic Int32 key read만 허용</x:v>
@@ -3104,16 +3104,16 @@
       </x:c>
       <x:c r="B58" s="4"/>
       <x:c r="C58" s="1" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="E58" s="1" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="D58" s="1" t="s">
+      <x:c r="F58" s="1" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="E58" s="1" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="F58" s="1" t="s">
-        <x:v>244</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>38</x:v>
@@ -3122,7 +3122,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I58" s="15" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="J58" s="16" t="str">
         <x:v>부분 구현: None/ACS static alias만 확인. true ACS/MCS/PCS 변환 미지원</x:v>
@@ -3133,19 +3133,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="4" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="C59" s="1" t="s">
+      <x:c r="E59" s="1" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="D59" s="1" t="s">
+      <x:c r="F59" s="1" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="E59" s="1" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="F59" s="1" t="s">
-        <x:v>250</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>38</x:v>
@@ -3154,7 +3154,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I59" s="15" t="s">
-        <x:v>251</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="J59" s="16" t="str">
         <x:v>부분 구현: axis status와 0x6041/0x6061 순차 read. Maestro atomic register와 비동등</x:v>
@@ -3165,14 +3165,14 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B60" s="4" t="s">
-        <x:v>252</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C60" s="1"/>
       <x:c r="D60" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="F60" s="1" t="s">
         <x:v>25</x:v>
@@ -3193,17 +3193,17 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B61" s="4" t="s">
-        <x:v>255</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C61" s="1"/>
       <x:c r="D61" s="1" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="E61" s="1" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="F61" s="1" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="E61" s="1" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="F61" s="1" t="s">
-        <x:v>258</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>16</x:v>
@@ -3212,7 +3212,7 @@
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="I61" s="15" t="s">
-        <x:v>259</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="J61" s="16" t="str">
         <x:v>25% 유지: SDK/wire/P1 완료. RAMex production NO-GO; 다음은 _FileSys A/B durable backend·RT exactly-once·실축 검증.</x:v>
@@ -3223,14 +3223,14 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B62" s="4" t="s">
-        <x:v>260</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C62" s="1"/>
       <x:c r="D62" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F62" s="1"/>
       <x:c r="G62" s="1" t="s">
@@ -3240,7 +3240,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I62" s="15" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="J62" s="16" t="str">
         <x:v>부분 구현: fixed X/Y/Z/U identity 검증만 수행. generic/dynamic kinematics 아님</x:v>
@@ -3251,14 +3251,14 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B63" s="4" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C63" s="1"/>
       <x:c r="D63" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="F63" s="1"/>
       <x:c r="G63" s="1" t="s">
@@ -3268,7 +3268,7 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I63" s="15" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="J63" s="16" t="str">
         <x:v>제한 활성: StopRecorder 구현. current image capture/cleanup qualification 필요</x:v>
@@ -3279,14 +3279,14 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B64" s="4" t="s">
-        <x:v>268</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C64" s="1"/>
       <x:c r="D64" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="F64" s="1"/>
       <x:c r="G64" s="1" t="s">
@@ -3296,7 +3296,7 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I64" s="15" t="s">
-        <x:v>270</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="J64" s="16" t="str">
         <x:v>제한 활성: status poll 구현. current image recorder live 필요</x:v>
@@ -3307,14 +3307,14 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B65" s="4" t="s">
-        <x:v>271</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C65" s="1"/>
       <x:c r="D65" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="F65" s="1"/>
       <x:c r="G65" s="1" t="s">
@@ -3324,7 +3324,7 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I65" s="15" t="s">
-        <x:v>273</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="J65" s="16" t="str">
         <x:v>제한 활성: Configure와 Start 구현. current image Single/Ring/Trigger live 필요</x:v>
@@ -3335,14 +3335,14 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B66" s="4" t="s">
-        <x:v>274</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C66" s="1"/>
       <x:c r="D66" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="F66" s="1"/>
       <x:c r="G66" s="1" t="s">
@@ -3352,7 +3352,7 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I66" s="15" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="J66" s="16" t="str">
         <x:v>제한 활성: header metadata 검증 구현. current image live 필요</x:v>
@@ -3363,14 +3363,14 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B67" s="4" t="s">
-        <x:v>277</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C67" s="1"/>
       <x:c r="D67" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="F67" s="1"/>
       <x:c r="G67" s="1" t="s">
@@ -3380,7 +3380,7 @@
         <x:v>0.75</x:v>
       </x:c>
       <x:c r="I67" s="15" t="s">
-        <x:v>279</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="J67" s="16" t="str">
         <x:v>제한 활성: chunk download와 byte count/SHA 검증 구현. current image live 필요</x:v>
@@ -3391,14 +3391,14 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B68" s="4" t="s">
-        <x:v>280</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C68" s="1"/>
       <x:c r="D68" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="F68" s="1"/>
       <x:c r="G68" s="1" t="s">
